--- a/data/trans_dic/P3A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tareas del hogar realizadas por el/la entrevistado/a</t>
+          <t>Tareas del hogar realizadas por el/la entrevistado/a (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,15; 41,71</t>
+          <t>27,01; 42,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,54; 46,56</t>
+          <t>30,89; 47,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,05; 36,83</t>
+          <t>20,98; 37,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84,42; 93,3</t>
+          <t>84,58; 93,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,61; 47,08</t>
+          <t>31,18; 45,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,89; 46,54</t>
+          <t>30,09; 45,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,9; 40,99</t>
+          <t>24,91; 41,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>86,58; 95,65</t>
+          <t>87,43; 95,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,35; 41,89</t>
+          <t>31,56; 41,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,76; 43,91</t>
+          <t>32,65; 43,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,77; 36,1</t>
+          <t>24,85; 36,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,63; 93,98</t>
+          <t>87,43; 93,64</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,75; 45,69</t>
+          <t>31,9; 45,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,62; 44,72</t>
+          <t>30,59; 43,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,86; 37,66</t>
+          <t>26,19; 37,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74,54; 89,46</t>
+          <t>75,7; 89,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,92; 43,6</t>
+          <t>30,87; 44,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,16; 41,4</t>
+          <t>29,23; 42,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,59; 36,05</t>
+          <t>25,18; 36,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>78,39; 87,02</t>
+          <t>78,21; 87,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,09; 42,62</t>
+          <t>33,04; 42,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31,26; 40,44</t>
+          <t>31,45; 40,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,38; 35,12</t>
+          <t>26,69; 34,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>80,05; 87,13</t>
+          <t>79,25; 87,0</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,32; 42,35</t>
+          <t>27,34; 41,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,29; 40,64</t>
+          <t>25,67; 40,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,0; 40,46</t>
+          <t>27,44; 40,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83,79; 94,22</t>
+          <t>83,89; 93,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,94; 41,94</t>
+          <t>27,41; 42,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,13; 43,62</t>
+          <t>29,76; 43,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,32; 43,87</t>
+          <t>29,82; 43,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81,88; 91,05</t>
+          <t>81,55; 91,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,44; 39,3</t>
+          <t>29,63; 40,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,94; 39,84</t>
+          <t>29,71; 39,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,43; 39,75</t>
+          <t>30,37; 40,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>84,42; 91,56</t>
+          <t>84,9; 91,64</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,8; 40,84</t>
+          <t>28,13; 40,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,23; 37,28</t>
+          <t>24,31; 37,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,85; 40,99</t>
+          <t>28,98; 41,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73,82; 85,22</t>
+          <t>74,0; 85,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,39; 40,05</t>
+          <t>27,68; 39,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,25; 35,36</t>
+          <t>22,0; 34,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,55; 40,51</t>
+          <t>27,9; 39,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79,74; 89,11</t>
+          <t>79,45; 89,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,27; 37,92</t>
+          <t>29,0; 38,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,05; 34,05</t>
+          <t>24,86; 33,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,67; 38,37</t>
+          <t>30,01; 38,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,53; 85,86</t>
+          <t>78,8; 85,97</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,87; 38,82</t>
+          <t>31,95; 38,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,84; 37,98</t>
+          <t>30,61; 37,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,1; 35,95</t>
+          <t>29,07; 35,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82,54; 88,56</t>
+          <t>82,32; 88,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,55; 39,17</t>
+          <t>32,64; 39,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,1; 37,21</t>
+          <t>30,38; 37,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,84; 36,52</t>
+          <t>30,09; 36,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>83,58; 88,14</t>
+          <t>83,7; 88,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,33; 37,99</t>
+          <t>33,34; 38,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,71; 36,52</t>
+          <t>31,76; 36,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,41; 35,26</t>
+          <t>30,42; 35,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>83,9; 87,61</t>
+          <t>83,95; 87,82</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tareas del hogar realizadas por el/la entrevistado/a (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>35883</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>37204</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25437</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>104795</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>45654</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>42255</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>33996</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>129701</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>81538</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>79458</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>59433</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>234497</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>28418; 44297</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29999; 46293</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18900; 33699</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99195; 109154</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>36877; 54208</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>33854; 50839</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>26071; 43165</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>122764; 134523</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>70536; 93133</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>68434; 91465</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>48407; 70572</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>225290; 241295</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>48145</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>48089</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48150</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>161845</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>52336</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>53896</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>52975</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>212055</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>100480</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>101986</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>101124</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>373901</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>39870; 56767</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39455; 56676</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39792; 57378</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>144219; 170577</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>43444; 61925</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>45181; 65411</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>44144; 63861</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>199467; 222449</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>87780; 112738</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>89171; 114215</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>87331; 114187</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>353093; 387626</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>37339</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34300</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>39112</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>170294</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>38509</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>42129</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>48848</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>161107</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>75848</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>76429</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>87960</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>331401</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>29489; 44844</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>26912; 42574</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>31977; 47450</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>159720; 178871</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>30858; 48023</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>34752; 51249</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>39609; 57707</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>151093; 169225</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>65309; 88640</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>65850; 88021</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>75732; 100127</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>318947; 344280</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>56671</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>44342</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>58286</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>134631</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>52184</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>43585</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>53114</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>153751</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>108855</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>87927</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>111400</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>288383</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>46511; 67433</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>35490; 55297</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>48348; 69671</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>124292; 143048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>43438; 62585</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>34094; 53431</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>44133; 62706</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>144001; 161458</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>93465; 122607</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>74815; 101533</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>97548; 125784</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>275155; 300207</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1655</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>178038</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>163934</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>170985</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>571565</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>188683</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>181865</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>188932</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>656615</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>366721</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>345800</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>359917</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1228181</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>160825; 194731</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>146023; 180617</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>152738; 189092</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>548406; 588993</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>172522; 206363</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>163677; 200904</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>171826; 209631</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>637741; 674181</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>344083; 397200</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>322566; 370197</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>333531; 387098</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1198846; 1254226</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P3A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,01; 42,1</t>
+          <t>27,05; 41,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,89; 47,66</t>
+          <t>30,37; 46,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,98; 37,41</t>
+          <t>20,26; 36,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84,58; 93,07</t>
+          <t>84,02; 93,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,18; 45,83</t>
+          <t>31,64; 45,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,09; 45,19</t>
+          <t>30,43; 45,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,91; 41,24</t>
+          <t>25,4; 41,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87,43; 95,81</t>
+          <t>87,27; 95,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,56; 41,67</t>
+          <t>31,11; 42,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,65; 43,63</t>
+          <t>32,45; 43,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,85; 36,24</t>
+          <t>25,59; 36,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,43; 93,64</t>
+          <t>87,51; 93,76</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,9; 45,43</t>
+          <t>31,57; 45,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,59; 43,94</t>
+          <t>30,89; 44,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,19; 37,77</t>
+          <t>26,02; 37,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,7; 89,54</t>
+          <t>75,78; 89,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,87; 44,0</t>
+          <t>30,84; 43,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,23; 42,32</t>
+          <t>28,92; 41,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,18; 36,43</t>
+          <t>24,88; 35,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>78,21; 87,22</t>
+          <t>78,03; 87,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,04; 42,43</t>
+          <t>32,8; 42,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31,45; 40,28</t>
+          <t>31,58; 40,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,69; 34,9</t>
+          <t>26,69; 35,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>79,25; 87,0</t>
+          <t>79,31; 87,33</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,34; 41,58</t>
+          <t>27,93; 41,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,67; 40,6</t>
+          <t>26,05; 40,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,44; 40,71</t>
+          <t>26,75; 40,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83,89; 93,94</t>
+          <t>83,4; 94,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,41; 42,66</t>
+          <t>26,95; 41,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,76; 43,88</t>
+          <t>29,52; 43,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,82; 43,44</t>
+          <t>30,21; 43,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81,55; 91,33</t>
+          <t>81,85; 90,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,63; 40,21</t>
+          <t>29,62; 39,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,71; 39,71</t>
+          <t>29,5; 39,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,37; 40,15</t>
+          <t>30,69; 39,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>84,9; 91,64</t>
+          <t>84,67; 91,66</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,13; 40,79</t>
+          <t>28,24; 41,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,31; 37,87</t>
+          <t>24,42; 37,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,98; 41,76</t>
+          <t>28,94; 41,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,0; 85,17</t>
+          <t>74,37; 85,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,68; 39,88</t>
+          <t>27,5; 39,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,0; 34,48</t>
+          <t>22,2; 34,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,9; 39,64</t>
+          <t>27,01; 39,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79,45; 89,09</t>
+          <t>79,23; 89,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,0; 38,04</t>
+          <t>29,37; 38,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,86; 33,74</t>
+          <t>25,02; 33,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,01; 38,7</t>
+          <t>30,12; 38,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,8; 85,97</t>
+          <t>78,95; 86,13</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,95; 38,69</t>
+          <t>32,07; 38,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,61; 37,87</t>
+          <t>31,15; 38,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,07; 35,99</t>
+          <t>29,41; 36,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82,32; 88,42</t>
+          <t>82,55; 88,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,64; 39,04</t>
+          <t>32,32; 39,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,38; 37,29</t>
+          <t>30,72; 37,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,09; 36,71</t>
+          <t>29,98; 36,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>83,7; 88,48</t>
+          <t>83,6; 88,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,34; 38,49</t>
+          <t>33,31; 37,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,76; 36,45</t>
+          <t>31,8; 36,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,42; 35,31</t>
+          <t>30,49; 34,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>83,95; 87,82</t>
+          <t>84,1; 87,7</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28418; 44297</t>
+          <t>28455; 44130</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29999; 46293</t>
+          <t>29497; 45067</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18900; 33699</t>
+          <t>18253; 32587</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99195; 109154</t>
+          <t>98534; 109496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36877; 54208</t>
+          <t>37432; 54401</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33854; 50839</t>
+          <t>34239; 51342</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26071; 43165</t>
+          <t>26591; 43040</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>122764; 134523</t>
+          <t>122534; 134651</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>70536; 93133</t>
+          <t>69541; 94088</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68434; 91465</t>
+          <t>68016; 91665</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48407; 70572</t>
+          <t>49839; 71815</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>225290; 241295</t>
+          <t>225502; 241625</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39870; 56767</t>
+          <t>39453; 57170</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39455; 56676</t>
+          <t>39838; 57250</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39792; 57378</t>
+          <t>39536; 57291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>144219; 170577</t>
+          <t>144370; 170818</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43444; 61925</t>
+          <t>43409; 61607</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45181; 65411</t>
+          <t>44698; 63983</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44144; 63861</t>
+          <t>43607; 62996</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>199467; 222449</t>
+          <t>199003; 221945</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87780; 112738</t>
+          <t>87139; 113619</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89171; 114215</t>
+          <t>89551; 115368</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>87331; 114187</t>
+          <t>87329; 115944</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>353093; 387626</t>
+          <t>353384; 389102</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29489; 44844</t>
+          <t>30117; 44402</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26912; 42574</t>
+          <t>27309; 42742</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31977; 47450</t>
+          <t>31178; 47031</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>159720; 178871</t>
+          <t>158788; 179542</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30858; 48023</t>
+          <t>30341; 46832</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34752; 51249</t>
+          <t>34477; 50357</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39609; 57707</t>
+          <t>40131; 58334</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>151093; 169225</t>
+          <t>151654; 168248</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>65309; 88640</t>
+          <t>65279; 87432</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65850; 88021</t>
+          <t>65377; 88085</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75732; 100127</t>
+          <t>76543; 99679</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>318947; 344280</t>
+          <t>318088; 344343</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46511; 67433</t>
+          <t>46693; 68002</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35490; 55297</t>
+          <t>35659; 54409</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48348; 69671</t>
+          <t>48282; 68851</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>124292; 143048</t>
+          <t>124909; 143132</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43438; 62585</t>
+          <t>43155; 62350</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34094; 53431</t>
+          <t>34404; 53389</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44133; 62706</t>
+          <t>42730; 62308</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>144001; 161458</t>
+          <t>143591; 161390</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93465; 122607</t>
+          <t>94647; 123073</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74815; 101533</t>
+          <t>75299; 102175</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>97548; 125784</t>
+          <t>97887; 125643</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>275155; 300207</t>
+          <t>275701; 300775</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>160825; 194731</t>
+          <t>161434; 195904</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>146023; 180617</t>
+          <t>148578; 181319</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>152738; 189092</t>
+          <t>154519; 189234</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>548406; 588993</t>
+          <t>549921; 590002</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>172522; 206363</t>
+          <t>170832; 207188</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>163677; 200904</t>
+          <t>165504; 202389</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>171826; 209631</t>
+          <t>171223; 207722</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>637741; 674181</t>
+          <t>637030; 673605</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>344083; 397200</t>
+          <t>343708; 389694</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>322566; 370197</t>
+          <t>323044; 373546</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>333531; 387098</t>
+          <t>334332; 382916</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1198846; 1254226</t>
+          <t>1200986; 1252460</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38,6%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37,56%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>32,48%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>92,15%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>34,11%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>38,3%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>28,24%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>89,35%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>38,6%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,56%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,48%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,96%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,05; 41,95</t>
+          <t>31,61; 47,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,37; 46,4</t>
+          <t>30,89; 46,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,26; 36,17</t>
+          <t>24,9; 40,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84,02; 93,36</t>
+          <t>86,8; 95,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,64; 45,99</t>
+          <t>26,15; 41,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,43; 45,64</t>
+          <t>30,54; 46,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,4; 41,12</t>
+          <t>21,05; 36,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87,27; 95,9</t>
+          <t>84,65; 93,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,11; 42,1</t>
+          <t>31,35; 41,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,45; 43,73</t>
+          <t>32,76; 43,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,59; 36,87</t>
+          <t>24,77; 36,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,51; 93,76</t>
+          <t>87,6; 93,87</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>37,19%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>34,87%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>30,22%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82,93%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>38,53%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>37,28%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>31,69%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>84,95%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>37,19%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>34,87%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>30,22%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,77%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,57; 45,75</t>
+          <t>30,92; 43,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,89; 44,39</t>
+          <t>29,16; 41,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,02; 37,71</t>
+          <t>24,59; 36,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,78; 89,66</t>
+          <t>78,11; 87,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,84; 43,77</t>
+          <t>31,75; 45,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,92; 41,4</t>
+          <t>30,62; 44,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,88; 35,94</t>
+          <t>25,86; 37,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>78,03; 87,03</t>
+          <t>81,99; 90,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,8; 42,76</t>
+          <t>33,09; 42,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31,58; 40,69</t>
+          <t>31,26; 40,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,69; 35,43</t>
+          <t>27,38; 35,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>79,31; 87,33</t>
+          <t>81,36; 87,48</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>34,21%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36,07%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36,77%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>86,75%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>34,62%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>32,71%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>33,56%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>89,44%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>34,21%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>36,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,77%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>87,77%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,93; 41,17</t>
+          <t>26,94; 41,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,05; 40,76</t>
+          <t>29,13; 43,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,75; 40,35</t>
+          <t>30,32; 43,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83,4; 94,3</t>
+          <t>81,46; 90,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,95; 41,6</t>
+          <t>27,32; 42,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,52; 43,12</t>
+          <t>25,29; 40,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,21; 43,91</t>
+          <t>27,0; 40,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81,85; 90,8</t>
+          <t>83,99; 92,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,62; 39,67</t>
+          <t>29,44; 39,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,5; 39,74</t>
+          <t>28,94; 39,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,69; 39,97</t>
+          <t>30,43; 39,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>84,67; 91,66</t>
+          <t>84,27; 90,93</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>33,25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28,13%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33,57%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>84,48%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>34,28%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>30,37%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>34,94%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>80,16%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>33,25%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,57%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,24; 41,13</t>
+          <t>27,39; 40,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,42; 37,27</t>
+          <t>22,25; 35,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,94; 41,27</t>
+          <t>27,55; 40,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,37; 85,22</t>
+          <t>79,5; 88,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,5; 39,73</t>
+          <t>27,8; 40,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,2; 34,46</t>
+          <t>24,23; 37,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,01; 39,38</t>
+          <t>28,85; 40,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79,23; 89,05</t>
+          <t>75,75; 86,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,37; 38,19</t>
+          <t>29,27; 37,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,02; 33,95</t>
+          <t>25,05; 34,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,12; 38,66</t>
+          <t>29,67; 38,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,95; 86,13</t>
+          <t>78,85; 85,96</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33,75%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>33,09%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>85,88%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>35,37%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>34,37%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>32,54%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>85,8%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>35,7%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>33,75%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>33,09%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,07; 38,92</t>
+          <t>32,55; 39,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,15; 38,02</t>
+          <t>30,1; 37,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,41; 36,02</t>
+          <t>29,84; 36,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82,55; 88,57</t>
+          <t>83,24; 87,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,32; 39,2</t>
+          <t>31,87; 38,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,72; 37,56</t>
+          <t>30,84; 37,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,98; 36,38</t>
+          <t>29,1; 35,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>83,6; 88,4</t>
+          <t>84,06; 88,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,31; 37,76</t>
+          <t>33,33; 37,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,8; 36,78</t>
+          <t>31,71; 36,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,49; 34,92</t>
+          <t>30,41; 35,26</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>84,1; 87,7</t>
+          <t>84,51; 87,73</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>175</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>45654</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42255</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33996</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>116020</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>35883</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>37204</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>25437</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>104795</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>45654</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>42255</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>33996</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>129701</t>
+          <t>108634</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>234497</t>
+          <t>224654</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28455; 44130</t>
+          <t>37390; 55693</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29497; 45067</t>
+          <t>34752; 52362</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18253; 32587</t>
+          <t>26062; 42905</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>98534; 109496</t>
+          <t>109284; 120230</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>37432; 54401</t>
+          <t>27514; 43883</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34239; 51342</t>
+          <t>29663; 45220</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26591; 43040</t>
+          <t>18964; 33178</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>122534; 134651</t>
+          <t>102481; 113337</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>69541; 94088</t>
+          <t>70067; 93625</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68016; 91665</t>
+          <t>68674; 92051</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49839; 71815</t>
+          <t>48236; 70317</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>225502; 241625</t>
+          <t>216354; 231848</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>245</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>52336</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>53896</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>52975</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>196710</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>48145</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>48089</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>48150</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>161845</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>52336</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>53896</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>52975</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>212055</t>
+          <t>160697</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>373901</t>
+          <t>357407</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39453; 57170</t>
+          <t>43519; 61363</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39838; 57250</t>
+          <t>45061; 63984</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39536; 57291</t>
+          <t>43099; 63202</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>144370; 170818</t>
+          <t>185282; 206710</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43409; 61607</t>
+          <t>39680; 57095</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44698; 63983</t>
+          <t>39493; 57682</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43607; 62996</t>
+          <t>39295; 57223</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>199003; 221945</t>
+          <t>151192; 167218</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87139; 113619</t>
+          <t>87923; 113251</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89551; 115368</t>
+          <t>88638; 114677</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>87329; 115944</t>
+          <t>89607; 114917</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>353384; 389102</t>
+          <t>343028; 368841</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>200</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>38509</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>42129</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>48848</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>146044</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>37339</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>34300</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>39112</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>170294</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>38509</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>42129</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>48848</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>161107</t>
+          <t>139564</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>331401</t>
+          <t>285607</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>30117; 44402</t>
+          <t>30326; 47212</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27309; 42742</t>
+          <t>34016; 50940</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31178; 47031</t>
+          <t>40281; 58282</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158788; 179542</t>
+          <t>137123; 153176</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30341; 46832</t>
+          <t>29460; 45670</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34477; 50357</t>
+          <t>26516; 42608</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40131; 58334</t>
+          <t>31470; 47159</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>151654; 168248</t>
+          <t>131908; 145486</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>65279; 87432</t>
+          <t>64889; 86632</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65377; 88085</t>
+          <t>64139; 88310</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76543; 99679</t>
+          <t>75884; 99148</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>318088; 344343</t>
+          <t>274199; 295863</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>196</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>52184</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>43585</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>53114</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>143092</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>56671</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>44342</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>58286</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>134631</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>52184</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>43585</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>53114</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>153751</t>
+          <t>136056</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>288383</t>
+          <t>279147</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46693; 68002</t>
+          <t>42985; 62852</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35659; 54409</t>
+          <t>34475; 54790</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48282; 68851</t>
+          <t>43582; 64086</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>124909; 143132</t>
+          <t>134652; 150486</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43155; 62350</t>
+          <t>45960; 67518</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34404; 53389</t>
+          <t>35375; 54435</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42730; 62308</t>
+          <t>48125; 68384</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>143591; 161390</t>
+          <t>126615; 143766</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>94647; 123073</t>
+          <t>94322; 122197</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75299; 102175</t>
+          <t>75396; 102472</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>97887; 125643</t>
+          <t>96454; 124731</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>275701; 300775</t>
+          <t>265343; 289257</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>253</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>816</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>839</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>188683</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>181865</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>188932</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>601865</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>178038</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>163934</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>170985</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>571565</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>188683</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>181865</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>188932</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>656615</t>
+          <t>544949</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1228181</t>
+          <t>1146816</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>161434; 195904</t>
+          <t>172022; 207056</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>148578; 181319</t>
+          <t>162166; 200479</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>154519; 189234</t>
+          <t>170425; 208535</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>549921; 590002</t>
+          <t>583378; 616585</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>170832; 207188</t>
+          <t>160422; 195426</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>165504; 202389</t>
+          <t>147102; 181161</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>171223; 207722</t>
+          <t>152883; 188892</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>637030; 673605</t>
+          <t>529290; 559406</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>343708; 389694</t>
+          <t>343940; 392042</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>323044; 373546</t>
+          <t>322120; 370964</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>334332; 382916</t>
+          <t>333384; 386607</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1200986; 1252460</t>
+          <t>1124354; 1167240</t>
         </is>
       </c>
     </row>
